--- a/summer_camps/021_summer_camper_registration_form--summer_camps.xlsx
+++ b/summer_camps/021_summer_camper_registration_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'physical_disability'}</t>
+          <t>physical_disability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Disability'}</t>
+          <t>Physical Disability</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chronic_illness'}</t>
+          <t>chronic_illness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chronic Illness'}</t>
+          <t>Chronic Illness</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'no_preference'}</t>
+          <t>no_preference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'No Preference'}</t>
+          <t>No Preference</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'espagnol'}</t>
+          <t>espagnol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Espagnol'}</t>
+          <t>Espagnol</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'intérmédiaire'}</t>
+          <t>intérmédiaire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Intérmédiaire'}</t>
+          <t>Intérmédiaire</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'intérmédiaire-expert'}</t>
+          <t>intérmédiaire-expert</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Intérmédiaire-Expert'}</t>
+          <t>Intérmédiaire-Expert</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'expert'}</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Expert'}</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'water_sports'}</t>
+          <t>water_sports</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Water Sports'}</t>
+          <t>Water Sports</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'arts_and_crafts'}</t>
+          <t>arts_and_crafts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Arts and Crafts'}</t>
+          <t>Arts and Crafts</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'théatre_et_performances'}</t>
+          <t>théatre_et_performances</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Théatre et Performances'}</t>
+          <t>Théatre et Performances</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'autres'}</t>
+          <t>autres</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Autres'}</t>
+          <t>Autres</t>
         </is>
       </c>
     </row>
